--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488167_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488167_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.699</v>
+        <v>12.113</v>
       </c>
       <c r="E2" t="n">
-        <v>8.2538</v>
+        <v>8.406499999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4452</v>
+        <v>3.7065</v>
       </c>
       <c r="G2" t="n">
         <v>5.1707</v>
@@ -610,13 +610,13 @@
         <v>2.9646</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8157</v>
+        <v>0.2297</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4216</v>
+        <v>0.5742</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3942</v>
+        <v>-0.3445</v>
       </c>
       <c r="V2" t="n">
         <v>5.6008</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.9526</v>
+        <v>7.0812</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3193</v>
+        <v>5.374</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6333</v>
+        <v>1.7071</v>
       </c>
       <c r="G3" t="n">
         <v>7.3211</v>
@@ -688,13 +688,13 @@
         <v>2.9646</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1558</v>
+        <v>-1.0272</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.5733</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.6743</v>
+        <v>-1.6005</v>
       </c>
       <c r="V3" t="n">
         <v>2.4548</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.0538</v>
+        <v>6.2557</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5128</v>
+        <v>4.6654</v>
       </c>
       <c r="F4" t="n">
-        <v>1.541</v>
+        <v>1.5902</v>
       </c>
       <c r="G4" t="n">
         <v>1.7863</v>
@@ -766,13 +766,13 @@
         <v>2.9646</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5405</v>
+        <v>-0.3386</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3121</v>
+        <v>0.4648</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8526</v>
+        <v>-0.8034</v>
       </c>
       <c r="V4" t="n">
         <v>2.7698</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. MAIGA</t>
+          <t>A. USAOLA REDONDO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6455</v>
+        <v>1.6874</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5505</v>
+        <v>2.0355</v>
       </c>
       <c r="F5" t="n">
-        <v>1.095</v>
+        <v>-0.3482</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3804</v>
+        <v>-0.6923</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1699</v>
+        <v>-0.9535</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2105</v>
+        <v>0.2611</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7409</v>
+        <v>-0.318</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2279</v>
+        <v>-0.318</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.487</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.6395</v>
+        <v>-0.3743</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.058</v>
+        <v>-0.6354</v>
       </c>
       <c r="O5" t="n">
-        <v>1.6974</v>
+        <v>0.2611</v>
       </c>
       <c r="P5" t="n">
         <v>0.3706</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2234</v>
+        <v>0.3706</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5306999999999999</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>1.348</v>
+        <v>-0.1641</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8173</v>
+        <v>-0.3445</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.6362</v>
+        <v>2.5177</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3144</v>
+        <v>2.5177</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.9506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. USAOLA REDONDO</t>
+          <t>G. MAIGA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5588</v>
+        <v>1.3775</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9808</v>
+        <v>0.0608</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.422</v>
+        <v>1.3166</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6923</v>
+        <v>2.3804</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9535</v>
+        <v>1.1699</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2611</v>
+        <v>1.2105</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.318</v>
+        <v>0.7409</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.318</v>
+        <v>1.2279</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.487</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3743</v>
+        <v>1.6395</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6354</v>
+        <v>-0.058</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2611</v>
+        <v>1.6974</v>
       </c>
       <c r="P6" t="n">
         <v>0.3706</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3706</v>
+        <v>2.2234</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6372</v>
+        <v>0.2627</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2189</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4183</v>
+        <v>-0.5957</v>
       </c>
       <c r="V6" t="n">
-        <v>2.5177</v>
+        <v>-1.6362</v>
       </c>
       <c r="W6" t="n">
-        <v>2.5177</v>
+        <v>0.3144</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.9506</v>
       </c>
     </row>
     <row r="7">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2089</v>
+        <v>-0.0858</v>
       </c>
       <c r="E8" t="n">
         <v>0.4897</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6986</v>
+        <v>-0.5755</v>
       </c>
       <c r="G8" t="n">
         <v>0.526</v>
@@ -1078,13 +1078,13 @@
         <v>0.1853</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9202</v>
+        <v>-0.7971</v>
       </c>
       <c r="T8" t="n">
         <v>-0.2189</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7014</v>
+        <v>-0.5783</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3976</v>
+        <v>-0.9802</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4515</v>
+        <v>-0.2557</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9461000000000001</v>
+        <v>-0.7245</v>
       </c>
       <c r="G9" t="n">
         <v>0.7687</v>
@@ -1156,13 +1156,13 @@
         <v>1.297</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.387</v>
+        <v>0.0305</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.06710000000000001</v>
+        <v>0.1287</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3198</v>
+        <v>-0.0982</v>
       </c>
       <c r="V9" t="n">
         <v>0.6294</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. CABALLERO CARPIO</t>
+          <t>F. GONZALEZ ROSCO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7919</v>
+        <v>-1.7822</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3964</v>
+        <v>0.2572</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3955</v>
+        <v>-2.0393</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0231</v>
+        <v>-0.2357</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.2382</v>
+        <v>-0.3203</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2152</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2198</v>
+        <v>0.3905</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2198</v>
+        <v>0.3905</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8033</v>
+        <v>-0.6263</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0184</v>
+        <v>-0.7108</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2152</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3706</v>
+        <v>0.7411</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3706</v>
+        <v>0.7411</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4544</v>
+        <v>-1.0287</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1766</v>
+        <v>-0.1334</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2778</v>
+        <v>-0.8954</v>
       </c>
       <c r="V10" t="n">
-        <v>0.315</v>
+        <v>-1.2589</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.315</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. GONZALEZ ROSCO</t>
+          <t>S. CABALLERO CARPIO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1263</v>
+        <v>-2.0874</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1592</v>
+        <v>-1.3964</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2855</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2357</v>
+        <v>-2.0231</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3203</v>
+        <v>-2.2382</v>
       </c>
       <c r="I11" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.2152</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3905</v>
+        <v>-1.2198</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3905</v>
+        <v>-1.2198</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6263</v>
+        <v>-0.8033</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7108</v>
+        <v>-1.0184</v>
       </c>
       <c r="O11" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.2152</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7411</v>
+        <v>0.3706</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7411</v>
+        <v>0.3706</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3729</v>
+        <v>-0.7499</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2313</v>
+        <v>-0.1766</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1416</v>
+        <v>-0.5733</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2589</v>
+        <v>0.315</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2589</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4747</v>
+        <v>-3.4692</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6934</v>
+        <v>-2.6387</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7812</v>
+        <v>-0.8305</v>
       </c>
       <c r="G12" t="n">
         <v>-1.3008</v>
@@ -1390,13 +1390,13 @@
         <v>0.9264</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.545</v>
+        <v>-1.5395</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5471</v>
+        <v>-0.4924</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9978</v>
+        <v>-1.0471</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6289</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.9919</v>
+        <v>-7.918</v>
       </c>
       <c r="E13" t="n">
         <v>-8.6592</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6673</v>
+        <v>0.7411</v>
       </c>
       <c r="G13" t="n">
         <v>-2.2031</v>
@@ -1468,13 +1468,13 @@
         <v>1.6676</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2965</v>
+        <v>-0.2226</v>
       </c>
       <c r="T13" t="n">
         <v>0.7374000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0339</v>
+        <v>-0.96</v>
       </c>
       <c r="V13" t="n">
         <v>0.2516</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>12.5625</v>
+        <v>12.8361</v>
       </c>
       <c r="E14" t="n">
-        <v>8.7097</v>
+        <v>8.983200000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>3.852900000000001</v>
+        <v>3.8525</v>
       </c>
       <c r="G14" t="n">
         <v>12.1423</v>
@@ -1546,13 +1546,13 @@
         <v>16.6758</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.9631</v>
+        <v>-5.6893</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8778</v>
+        <v>2.1514</v>
       </c>
       <c r="U14" t="n">
-        <v>-7.840599999999999</v>
+        <v>-7.8409</v>
       </c>
       <c r="V14" t="n">
         <v>11.0151</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0676</v>
+        <v>3.4376</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0214</v>
+        <v>2.14</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0462</v>
+        <v>1.2977</v>
       </c>
       <c r="G15" t="n">
         <v>-0.275</v>
@@ -1624,13 +1624,13 @@
         <v>3.3352</v>
       </c>
       <c r="S15" t="n">
-        <v>2.0603</v>
+        <v>1.4304</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9176</v>
+        <v>1.0362</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1427</v>
+        <v>0.3942</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1264</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5898</v>
+        <v>2.2839</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5796</v>
+        <v>-0.4817</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1694</v>
+        <v>2.7656</v>
       </c>
       <c r="G16" t="n">
         <v>-0.4425</v>
@@ -1702,13 +1702,13 @@
         <v>3.7057</v>
       </c>
       <c r="S16" t="n">
-        <v>0.252</v>
+        <v>0.946</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8307</v>
+        <v>0.9286</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5788</v>
+        <v>0.0174</v>
       </c>
       <c r="V16" t="n">
         <v>2.7068</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1418</v>
+        <v>1.5994</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1819</v>
+        <v>-0.0839</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3237</v>
+        <v>1.6833</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2324</v>
@@ -1780,13 +1780,13 @@
         <v>1.1117</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8914</v>
+        <v>1.3489</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8891</v>
+        <v>0.9871</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0022</v>
+        <v>0.3619</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6289</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Á. LLAMAS JIMENEZ</t>
+          <t>A. MARQUEZ MARQUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3221</v>
+        <v>0.5566</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3221</v>
+        <v>-0.8507</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1.4073</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3221</v>
+        <v>-2.6211</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3221</v>
+        <v>0.0272</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-2.6484</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3221</v>
+        <v>-0.5618</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3221</v>
+        <v>2.0176</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-2.5794</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-2.0594</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-1.9904</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.7057</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.1189</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.2321</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0.1132</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.1324</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2583</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.1259</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. BENÍTEZ SIERRA</t>
+          <t>Á. LLAMAS JIMENEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. MORILLO LEON</t>
+          <t>F. BENÍTEZ SIERRA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,37 +1969,37 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2147</v>
+        <v>0.3221</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.3221</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2147</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2147</v>
+        <v>0.3221</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2147</v>
+        <v>0.3221</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.3221</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.3221</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2147</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2147</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. MARQUEZ MARQUEZ</t>
+          <t>D. MORILLO LEON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5292</v>
+        <v>-0.2147</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3403</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8111</v>
+        <v>-0.2147</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.6211</v>
+        <v>-0.2147</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0272</v>
+        <v>-0.2147</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.6484</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5618</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>2.0176</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.5794</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0594</v>
+        <v>-0.2147</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.9904</v>
+        <v>-0.2147</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3.7057</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0331</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7423999999999999</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7093</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.1324</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2583</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3919</v>
+        <v>-0.4768</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1686</v>
+        <v>1.7562</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5605</v>
+        <v>-2.233</v>
       </c>
       <c r="G22" t="n">
         <v>0.6637999999999999</v>
@@ -2170,13 +2170,13 @@
         <v>1.8529</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0241</v>
+        <v>0.891</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1816</v>
+        <v>0.7691</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2057</v>
+        <v>0.1219</v>
       </c>
       <c r="V22" t="n">
         <v>-2.958</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4312</v>
+        <v>-1.6282</v>
       </c>
       <c r="E23" t="n">
         <v>1.0306</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4618</v>
+        <v>-2.6588</v>
       </c>
       <c r="G23" t="n">
         <v>-0.7321</v>
@@ -2248,13 +2248,13 @@
         <v>1.4823</v>
       </c>
       <c r="S23" t="n">
-        <v>1.2627</v>
+        <v>1.0657</v>
       </c>
       <c r="T23" t="n">
         <v>0.7796999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.483</v>
+        <v>0.286</v>
       </c>
       <c r="V23" t="n">
         <v>-2.5177</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. BRAVO ORTEGA</t>
+          <t>I. PEREZ SAENZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.679</v>
+        <v>-2.0694</v>
       </c>
       <c r="E24" t="n">
-        <v>2.6537</v>
+        <v>-0.5117</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.3327</v>
+        <v>-1.5577</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.9517</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3592</v>
+        <v>-0.4294</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2472</v>
+        <v>-0.5223</v>
       </c>
       <c r="J24" t="n">
-        <v>1.9463</v>
+        <v>-0.6529</v>
       </c>
       <c r="K24" t="n">
-        <v>1.8633</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0829</v>
+        <v>-0.6529</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.5527</v>
+        <v>-0.2989</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.2225</v>
+        <v>-0.4294</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3301</v>
+        <v>0.1306</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.7793</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.5155</v>
+        <v>0.1411</v>
       </c>
       <c r="T24" t="n">
-        <v>3.1723</v>
+        <v>0.1411</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6568000000000001</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.588</v>
+        <v>-1.2589</v>
       </c>
       <c r="W24" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.9024</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>I. PEREZ SAENZ</t>
+          <t>Y. VAQUERO HERNANDEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.2653</v>
+        <v>-2.817</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.7076</v>
+        <v>-1.6396</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.5577</v>
+        <v>-1.1774</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.9517</v>
+        <v>-1.9981</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.4294</v>
+        <v>-1.9858</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5223</v>
+        <v>-0.0123</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.6529</v>
+        <v>-1.2092</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>-1.2198</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.6529</v>
+        <v>0.0107</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.2989</v>
+        <v>-0.789</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.4294</v>
+        <v>-0.766</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1306</v>
+        <v>-0.023</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>0.7411</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0547</v>
+        <v>0.3109</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0547</v>
+        <v>0.1816</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>0.1293</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.2589</v>
+        <v>-0.9444</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X25" t="n">
         <v>-1.2589</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Y. VAQUERO HERNANDEZ</t>
+          <t>M. BRAVO ORTEGA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.9401</v>
+        <v>-3.2052</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.6396</v>
+        <v>0.891</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.3005</v>
+        <v>-4.0961</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.9981</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.9858</v>
+        <v>-0.3592</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0123</v>
+        <v>-0.2472</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.2092</v>
+        <v>1.9463</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.2198</v>
+        <v>1.8633</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0107</v>
+        <v>0.0829</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.789</v>
+        <v>-2.5527</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.766</v>
+        <v>-2.2225</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.023</v>
+        <v>-0.3301</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.9264</v>
+        <v>-2.7793</v>
       </c>
       <c r="R26" t="n">
-        <v>0.7411</v>
+        <v>2.7793</v>
       </c>
       <c r="S26" t="n">
-        <v>0.1878</v>
+        <v>0.9893</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1816</v>
+        <v>1.4096</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0062</v>
+        <v>-0.4203</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.9444</v>
+        <v>-3.588</v>
       </c>
       <c r="W26" t="n">
         <v>0.3144</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.2589</v>
+        <v>-3.9024</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-9.554399999999999</v>
+        <v>-8.061400000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.9222</v>
+        <v>-6.747</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.6322</v>
+        <v>-1.3143</v>
       </c>
       <c r="G27" t="n">
         <v>-5.376</v>
@@ -2560,13 +2560,13 @@
         <v>2.594</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.161</v>
+        <v>0.332</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.7996</v>
+        <v>0.3756</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.3614</v>
+        <v>-0.0435</v>
       </c>
       <c r="V27" t="n">
         <v>-2.8321</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-12.5624</v>
+        <v>-9.951000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.8527</v>
+        <v>-3.8526</v>
       </c>
       <c r="F28" t="n">
-        <v>-8.709699999999998</v>
+        <v>-6.0981</v>
       </c>
       <c r="G28" t="n">
         <v>-12.142</v>
@@ -2608,16 +2608,16 @@
         <v>-2.2342</v>
       </c>
       <c r="I28" t="n">
-        <v>-9.907900000000001</v>
+        <v>-9.9079</v>
       </c>
       <c r="J28" t="n">
         <v>-1.3097</v>
       </c>
       <c r="K28" t="n">
-        <v>7.485600000000002</v>
+        <v>7.4856</v>
       </c>
       <c r="L28" t="n">
-        <v>-8.7951</v>
+        <v>-8.795099999999998</v>
       </c>
       <c r="M28" t="n">
         <v>-10.8327</v>
@@ -2638,13 +2638,13 @@
         <v>21.3079</v>
       </c>
       <c r="S28" t="n">
-        <v>5.962999999999999</v>
+        <v>8.574200000000001</v>
       </c>
       <c r="T28" t="n">
         <v>7.8407</v>
       </c>
       <c r="U28" t="n">
-        <v>-1.8779</v>
+        <v>0.7337</v>
       </c>
       <c r="V28" t="n">
         <v>-11.0152</v>
